--- a/314e-ig/output/StructureDefinition-datetime-precision-314e.xlsx
+++ b/314e-ig/output/StructureDefinition-datetime-precision-314e.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-16T16:45:26+05:30</t>
+    <t>2026-05-17T00:25:02+05:30</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -84,9 +84,8 @@
     <t>Description</t>
   </si>
   <si>
-    <t>Specifies the meaningful precision of a dateTime value when the base
-FHIR dateTime datatype permits greater precision than is actually known,
-verified, or clinically usable.
+    <t>Specifies the meaningful/ usable precision of a dateTime value when the 
+datatype syntactically permits greater precision than is actually known or clinically usable.
 This extension is intended to explicitly communicate the usable precision
 of a dateTime value, such as year-only, year-month, date-only, or
 full timestamp precision.
@@ -262,7 +261,7 @@
     <t>Usable precision of a dateTime value</t>
   </si>
   <si>
-    <t>This extension communicates the meaningful precision of a dateTime value
+    <t>This extension communicates the meaningful and usable precision of a dateTime value
 when the datatype syntactically allows more precision than is actually known
 or appropriate to use.
 For example:
@@ -270,7 +269,7 @@
 - Only the date may be verified without time
 - Only month/year may be clinically relevant
 This extension SHALL NOT alter the actual dateTime value itself,
-but instead clarifies the degree of confidence or precision
+but instead clarifies the degree of precision
 associated with the recorded value.</t>
   </si>
   <si>
@@ -353,11 +352,11 @@
 </t>
   </si>
   <si>
-    <t>Meaningful usable precision of the dateTime value</t>
-  </si>
-  <si>
-    <t>Indicates the precision that is clinically, operationally,
-or semantically meaningful for the associated dateTime value.
+    <t>Known/ usable precision of the dateTime value</t>
+  </si>
+  <si>
+    <t>Indicates the precision that is operationally
+or semantically meaningful/ usable for the associated dateTime value.
 Examples include year-only, month-level, date-level,
 or full timestamp precision.</t>
   </si>

--- a/314e-ig/output/StructureDefinition-datetime-precision-314e.xlsx
+++ b/314e-ig/output/StructureDefinition-datetime-precision-314e.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-17T00:25:02+05:30</t>
+    <t>2026-05-19T06:46:39+05:30</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/314e-ig/output/StructureDefinition-datetime-precision-314e.xlsx
+++ b/314e-ig/output/StructureDefinition-datetime-precision-314e.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-19T06:46:39+05:30</t>
+    <t>2026-05-19T11:54:54+05:30</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/314e-ig/output/StructureDefinition-datetime-precision-314e.xlsx
+++ b/314e-ig/output/StructureDefinition-datetime-precision-314e.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-19T11:54:54+05:30</t>
+    <t>2026-05-25T12:07:44+05:30</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/314e-ig/output/StructureDefinition-datetime-precision-314e.xlsx
+++ b/314e-ig/output/StructureDefinition-datetime-precision-314e.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-25T12:07:44+05:30</t>
+    <t>2026-05-25T12:34:12+05:30</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/314e-ig/output/StructureDefinition-datetime-precision-314e.xlsx
+++ b/314e-ig/output/StructureDefinition-datetime-precision-314e.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-25T12:34:12+05:30</t>
+    <t>2026-05-25T13:52:53+05:30</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/314e-ig/output/StructureDefinition-datetime-precision-314e.xlsx
+++ b/314e-ig/output/StructureDefinition-datetime-precision-314e.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-25T13:52:53+05:30</t>
+    <t>2026-05-25T14:14:21+05:30</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/314e-ig/output/StructureDefinition-datetime-precision-314e.xlsx
+++ b/314e-ig/output/StructureDefinition-datetime-precision-314e.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-25T14:14:21+05:30</t>
+    <t>2026-05-25T14:26:28+05:30</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/314e-ig/output/StructureDefinition-datetime-precision-314e.xlsx
+++ b/314e-ig/output/StructureDefinition-datetime-precision-314e.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-25T14:26:28+05:30</t>
+    <t>2026-05-25T14:41:34+05:30</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/314e-ig/output/StructureDefinition-datetime-precision-314e.xlsx
+++ b/314e-ig/output/StructureDefinition-datetime-precision-314e.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-25T14:41:34+05:30</t>
+    <t>2026-05-25T15:12:42+05:30</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/314e-ig/output/StructureDefinition-datetime-precision-314e.xlsx
+++ b/314e-ig/output/StructureDefinition-datetime-precision-314e.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-25T15:12:42+05:30</t>
+    <t>2026-05-25T15:24:41+05:30</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/314e-ig/output/StructureDefinition-datetime-precision-314e.xlsx
+++ b/314e-ig/output/StructureDefinition-datetime-precision-314e.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-25T15:24:41+05:30</t>
+    <t>2026-05-25T15:48:57+05:30</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/314e-ig/output/StructureDefinition-datetime-precision-314e.xlsx
+++ b/314e-ig/output/StructureDefinition-datetime-precision-314e.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-25T15:48:57+05:30</t>
+    <t>2026-05-25T16:36:06+05:30</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/314e-ig/output/StructureDefinition-datetime-precision-314e.xlsx
+++ b/314e-ig/output/StructureDefinition-datetime-precision-314e.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-25T16:36:06+05:30</t>
+    <t>2026-05-26T08:48:22+05:30</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/314e-ig/output/StructureDefinition-datetime-precision-314e.xlsx
+++ b/314e-ig/output/StructureDefinition-datetime-precision-314e.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-26T08:48:22+05:30</t>
+    <t>2026-05-26T12:06:33+05:30</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/314e-ig/output/StructureDefinition-datetime-precision-314e.xlsx
+++ b/314e-ig/output/StructureDefinition-datetime-precision-314e.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-26T12:06:33+05:30</t>
+    <t>2026-05-26T19:54:55+05:30</t>
   </si>
   <si>
     <t>Publisher</t>
